--- a/templates/public_holiday_overtime_template.xlsx
+++ b/templates/public_holiday_overtime_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\wordtoexcel\staff_manager\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\dev\projects\wordtoexcel\staff_manager\frontend\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D39C3844-7159-4B8B-9B13-309445B9D38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C778237D-D6C4-4DCF-BA3B-DAB3AF8FF701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-870" yWindow="5565" windowWidth="30435" windowHeight="18705" xr2:uid="{470BC3E8-F96E-4CB7-BC26-3E2C09320104}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{470BC3E8-F96E-4CB7-BC26-3E2C09320104}"/>
   </bookViews>
   <sheets>
     <sheet name="國定假日加班確認單" sheetId="1" r:id="rId1"/>
@@ -414,7 +414,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -491,15 +491,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -668,41 +659,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thick">
         <color indexed="64"/>
       </right>
@@ -751,21 +707,225 @@
     </border>
     <border>
       <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -777,188 +937,230 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1300,529 +1502,529 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="36"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
     </row>
     <row r="2" spans="1:15" ht="25.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="43"/>
+      <c r="C2" s="14"/>
       <c r="D2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="43"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="14"/>
       <c r="I2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="37" t="s">
+      <c r="J2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="46"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="53" t="s">
+      <c r="K2" s="15"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="37" t="s">
+      <c r="N2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="38"/>
+      <c r="O2" s="9"/>
     </row>
     <row r="3" spans="1:15" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="42"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="45"/>
+      <c r="A3" s="13"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="18"/>
       <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="47"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="49"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="18"/>
       <c r="I3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="39"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="54"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="40"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="11"/>
     </row>
     <row r="4" spans="1:15" ht="39.6" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="31" t="s">
+      <c r="D4" s="26"/>
+      <c r="E4" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="32"/>
-      <c r="G4" s="3" t="s">
+      <c r="F4" s="28"/>
+      <c r="G4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="30" t="s">
+      <c r="I4" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="30"/>
-      <c r="K4" s="33" t="s">
+      <c r="J4" s="74"/>
+      <c r="K4" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="34"/>
+      <c r="L4" s="28"/>
       <c r="M4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="O4" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="15"/>
+      <c r="B5" s="54"/>
       <c r="C5" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="56"/>
-      <c r="E5" s="20" t="s">
+      <c r="D5" s="34"/>
+      <c r="E5" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="28"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="20" t="s">
+      <c r="H5" s="32"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="M5" s="59" t="s">
+      <c r="M5" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="N5" s="24"/>
-      <c r="O5" s="13"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="59"/>
     </row>
     <row r="6" spans="1:15" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="10" t="s">
+      <c r="A6" s="30"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="28"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="10" t="s">
+      <c r="H6" s="35"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="M6" s="60"/>
-      <c r="N6" s="24"/>
-      <c r="O6" s="13"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="33"/>
+      <c r="O6" s="29"/>
     </row>
     <row r="7" spans="1:15" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="27"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="13"/>
+      <c r="A7" s="30"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="67"/>
+      <c r="K7" s="61"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="33"/>
+      <c r="O7" s="29"/>
     </row>
     <row r="8" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="13"/>
+      <c r="A8" s="30"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="71"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="67"/>
+      <c r="K8" s="65"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="33"/>
+      <c r="O8" s="29"/>
     </row>
     <row r="9" spans="1:15" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="24"/>
-      <c r="O9" s="13"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="67"/>
+      <c r="K9" s="61"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="29"/>
     </row>
     <row r="10" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="27"/>
-      <c r="N10" s="24"/>
-      <c r="O10" s="13"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="67"/>
+      <c r="K10" s="65"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="29"/>
     </row>
     <row r="11" spans="1:15" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="20"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="24"/>
-      <c r="O11" s="13"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="61"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="33"/>
+      <c r="O11" s="29"/>
     </row>
     <row r="12" spans="1:15" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="27"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="13"/>
+      <c r="A12" s="30"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="67"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="40"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="33"/>
+      <c r="O12" s="29"/>
     </row>
     <row r="13" spans="1:15" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="24"/>
-      <c r="O13" s="13"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="67"/>
+      <c r="K13" s="61"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="33"/>
+      <c r="O13" s="29"/>
     </row>
     <row r="14" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="13"/>
+      <c r="A14" s="30"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="67"/>
+      <c r="K14" s="65"/>
+      <c r="L14" s="40"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="29"/>
     </row>
     <row r="15" spans="1:15" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="27"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="13"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="67"/>
+      <c r="K15" s="61"/>
+      <c r="L15" s="40"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="33"/>
+      <c r="O15" s="29"/>
     </row>
     <row r="16" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="27"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="13"/>
+      <c r="A16" s="30"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="67"/>
+      <c r="K16" s="65"/>
+      <c r="L16" s="40"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="29"/>
     </row>
     <row r="17" spans="1:15" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="27"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="13"/>
+      <c r="A17" s="30"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="67"/>
+      <c r="K17" s="61"/>
+      <c r="L17" s="40"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="33"/>
+      <c r="O17" s="29"/>
     </row>
     <row r="18" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="14"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="25"/>
-      <c r="K18" s="26"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="27"/>
-      <c r="N18" s="24"/>
-      <c r="O18" s="13"/>
+      <c r="A18" s="30"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="67"/>
+      <c r="K18" s="65"/>
+      <c r="L18" s="40"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="29"/>
     </row>
     <row r="19" spans="1:15" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="27"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="13"/>
+      <c r="A19" s="30"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="67"/>
+      <c r="K19" s="61"/>
+      <c r="L19" s="40"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="33"/>
+      <c r="O19" s="29"/>
     </row>
     <row r="20" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="26"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="13"/>
+      <c r="A20" s="30"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="67"/>
+      <c r="K20" s="65"/>
+      <c r="L20" s="40"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="33"/>
+      <c r="O20" s="29"/>
     </row>
     <row r="21" spans="1:15" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="27"/>
-      <c r="N21" s="24"/>
-      <c r="O21" s="13"/>
-    </row>
-    <row r="22" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="26"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="27"/>
-      <c r="N22" s="24"/>
-      <c r="O22" s="13"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
+      <c r="A21" s="30"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="63"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="67"/>
+      <c r="K21" s="61"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="29"/>
+    </row>
+    <row r="22" spans="1:15" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="44"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="64"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="66"/>
+      <c r="L22" s="47"/>
+      <c r="M22" s="51"/>
+      <c r="N22" s="50"/>
+      <c r="O22" s="52"/>
+    </row>
+    <row r="23" spans="1:15" ht="17.25" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
-      <c r="O23" s="12"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="38"/>
+      <c r="N23" s="38"/>
+      <c r="O23" s="38"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
-      <c r="N24" s="12"/>
-      <c r="O24" s="12"/>
+      <c r="A24" s="38"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="38"/>
+      <c r="O24" s="38"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="12"/>
-      <c r="O25" s="12"/>
+      <c r="A25" s="38"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="38"/>
+      <c r="M25" s="38"/>
+      <c r="N25" s="38"/>
+      <c r="O25" s="38"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
-      <c r="N26" s="12"/>
-      <c r="O26" s="12"/>
+      <c r="A26" s="38"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="38"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="38"/>
+      <c r="O26" s="38"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
+      <c r="A27" s="38"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="38"/>
+      <c r="L27" s="38"/>
+      <c r="M27" s="38"/>
+      <c r="N27" s="38"/>
+      <c r="O27" s="38"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
@@ -1831,47 +2033,43 @@
     </row>
   </sheetData>
   <mergeCells count="94">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="N2:O3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:C3"/>
-    <mergeCell ref="E2:H3"/>
-    <mergeCell ref="J2:L3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:J8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="A5:B6"/>
-    <mergeCell ref="C5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:J6"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="N9:N10"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="A9:B10"/>
-    <mergeCell ref="C9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="A23:O27"/>
+    <mergeCell ref="O19:O20"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="C21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="I21:J22"/>
+    <mergeCell ref="K21:K22"/>
+    <mergeCell ref="M21:M22"/>
+    <mergeCell ref="N21:N22"/>
+    <mergeCell ref="O21:O22"/>
+    <mergeCell ref="N17:N18"/>
+    <mergeCell ref="O17:O18"/>
+    <mergeCell ref="A19:B20"/>
+    <mergeCell ref="C19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="I19:J20"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="M15:M16"/>
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="I17:J18"/>
+    <mergeCell ref="K17:K18"/>
+    <mergeCell ref="M17:M18"/>
+    <mergeCell ref="A15:B16"/>
+    <mergeCell ref="C15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="I15:J16"/>
+    <mergeCell ref="K15:K16"/>
     <mergeCell ref="O9:O10"/>
     <mergeCell ref="O11:O12"/>
     <mergeCell ref="A13:B14"/>
@@ -1888,46 +2086,50 @@
     <mergeCell ref="E11:E12"/>
     <mergeCell ref="H11:H12"/>
     <mergeCell ref="I11:J12"/>
-    <mergeCell ref="M15:M16"/>
-    <mergeCell ref="N15:N16"/>
-    <mergeCell ref="O15:O16"/>
-    <mergeCell ref="A17:B18"/>
-    <mergeCell ref="C17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="I17:J18"/>
-    <mergeCell ref="K17:K18"/>
-    <mergeCell ref="M17:M18"/>
-    <mergeCell ref="A15:B16"/>
-    <mergeCell ref="C15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="I15:J16"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="N17:N18"/>
-    <mergeCell ref="O17:O18"/>
-    <mergeCell ref="A19:B20"/>
-    <mergeCell ref="C19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="I19:J20"/>
-    <mergeCell ref="K19:K20"/>
-    <mergeCell ref="M19:M20"/>
-    <mergeCell ref="N19:N20"/>
-    <mergeCell ref="A23:O27"/>
-    <mergeCell ref="O19:O20"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="C21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="I21:J22"/>
-    <mergeCell ref="K21:K22"/>
-    <mergeCell ref="M21:M22"/>
-    <mergeCell ref="N21:N22"/>
-    <mergeCell ref="O21:O22"/>
+    <mergeCell ref="A9:B10"/>
+    <mergeCell ref="C9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:J8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="A5:B6"/>
+    <mergeCell ref="C5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:J6"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="N2:O3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="E2:H3"/>
+    <mergeCell ref="J2:L3"/>
+    <mergeCell ref="M2:M3"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.35433070866141736" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="69" fitToHeight="0" orientation="landscape" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="69" orientation="landscape" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>